--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/6148-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/6148-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7E81F45F-73AB-470F-9D06-97A2C4CBF458}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{901C5AFE-71D8-486B-8769-D014A632FE99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{D871601E-B629-46FD-9628-AC6933FE52EE}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{DB9D700F-220A-41C0-AD3C-35E32F56C357}"/>
   </bookViews>
   <sheets>
     <sheet name="6148-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1496,30 +1496,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E8C385C-C0AE-4702-8808-3744BD28E4C3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35F6682C-CFE6-4B7C-89D1-100A8EE9D9C9}">
   <dimension ref="A1:X60"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="7" width="7.125" customWidth="1"/>
-    <col min="8" max="8" width="6.75" customWidth="1"/>
-    <col min="9" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.5" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="7" width="6.109375" customWidth="1"/>
+    <col min="8" max="8" width="5.88671875" customWidth="1"/>
+    <col min="9" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -1553,7 +1553,7 @@
       <c r="W1" s="29"/>
       <c r="X1" s="21"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="22" t="s">
         <v>1</v>
       </c>
@@ -1589,7 +1589,7 @@
       <c r="W2" s="31"/>
       <c r="X2" s="32"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="22" t="s">
         <v>2</v>
       </c>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="X3" s="35"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="24"/>
       <c r="B4" s="25"/>
       <c r="C4" s="7"/>
@@ -1709,7 +1709,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="36">
         <v>2025</v>
       </c>
@@ -1781,7 +1781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1855,7 +1855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>29</v>
       </c>
@@ -1929,7 +1929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>29</v>
       </c>
@@ -2003,7 +2003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>29</v>
       </c>
@@ -2077,7 +2077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="38">
         <v>2024</v>
       </c>
@@ -2149,7 +2149,7 @@
         <v>5.55</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>29</v>
       </c>
@@ -2223,7 +2223,7 @@
         <v>5.55</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
         <v>29</v>
       </c>
@@ -2297,7 +2297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
         <v>29</v>
       </c>
@@ -2371,7 +2371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
         <v>29</v>
       </c>
@@ -2445,7 +2445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>29</v>
       </c>
@@ -2519,7 +2519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="36">
         <v>2023</v>
       </c>
@@ -2591,7 +2591,7 @@
         <v>5.73</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>29</v>
       </c>
@@ -2665,7 +2665,7 @@
         <v>5.73</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>29</v>
       </c>
@@ -2739,7 +2739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>29</v>
       </c>
@@ -2813,7 +2813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
         <v>29</v>
       </c>
@@ -2887,7 +2887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>29</v>
       </c>
@@ -2961,7 +2961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="38">
         <v>2022</v>
       </c>
@@ -3033,7 +3033,7 @@
         <v>6.06</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="16" t="s">
         <v>29</v>
       </c>
@@ -3107,7 +3107,7 @@
         <v>6.06</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="16" t="s">
         <v>29</v>
       </c>
@@ -3181,7 +3181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="16" t="s">
         <v>29</v>
       </c>
@@ -3255,7 +3255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="16" t="s">
         <v>29</v>
       </c>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="16" t="s">
         <v>29</v>
       </c>
@@ -3403,7 +3403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="36">
         <v>2021</v>
       </c>
@@ -3475,7 +3475,7 @@
         <v>9.44</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="11" t="s">
         <v>29</v>
       </c>
@@ -3549,7 +3549,7 @@
         <v>9.44</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="s">
         <v>29</v>
       </c>
@@ -3623,7 +3623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="11" t="s">
         <v>29</v>
       </c>
@@ -3697,7 +3697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="11" t="s">
         <v>29</v>
       </c>
@@ -3771,7 +3771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="11" t="s">
         <v>29</v>
       </c>
@@ -3845,7 +3845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="38">
         <v>2020</v>
       </c>
@@ -3917,7 +3917,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="16" t="s">
         <v>29</v>
       </c>
@@ -3991,7 +3991,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="16" t="s">
         <v>29</v>
       </c>
@@ -4065,7 +4065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="16" t="s">
         <v>29</v>
       </c>
@@ -4139,7 +4139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="36">
         <v>2019</v>
       </c>
@@ -4211,7 +4211,7 @@
         <v>4.78</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="38">
         <v>2018</v>
       </c>
@@ -4283,7 +4283,7 @@
         <v>10.9</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="36">
         <v>2017</v>
       </c>
@@ -4355,7 +4355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="38">
         <v>2016</v>
       </c>
@@ -4427,7 +4427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="36">
         <v>2015</v>
       </c>
@@ -4499,7 +4499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="38">
         <v>2014</v>
       </c>
@@ -4571,7 +4571,7 @@
         <v>7.71</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="36">
         <v>2013</v>
       </c>
@@ -4643,7 +4643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="38">
         <v>2012</v>
       </c>
@@ -4715,7 +4715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="36">
         <v>2011</v>
       </c>
@@ -4787,7 +4787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="38">
         <v>2010</v>
       </c>
@@ -4859,7 +4859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="36">
         <v>2009</v>
       </c>
@@ -4931,7 +4931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="38">
         <v>2008</v>
       </c>
@@ -5003,7 +5003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="36">
         <v>2007</v>
       </c>
@@ -5075,7 +5075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A51" s="38">
         <v>2006</v>
       </c>
@@ -5147,7 +5147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A52" s="36">
         <v>2005</v>
       </c>
@@ -5219,7 +5219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A53" s="38">
         <v>2004</v>
       </c>
@@ -5291,7 +5291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A54" s="36">
         <v>2003</v>
       </c>
@@ -5363,7 +5363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A55" s="38">
         <v>2002</v>
       </c>
@@ -5435,7 +5435,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="56" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A56" s="36">
         <v>2001</v>
       </c>
@@ -5507,7 +5507,7 @@
         <v>9.31</v>
       </c>
     </row>
-    <row r="57" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A57" s="38">
         <v>2000</v>
       </c>
@@ -5579,7 +5579,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="58" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A58" s="36">
         <v>1999</v>
       </c>
@@ -5651,7 +5651,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="59" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A59" s="38">
         <v>1998</v>
       </c>
@@ -5723,7 +5723,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="60" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A60" s="36" t="s">
         <v>52</v>
       </c>
